--- a/evaluation_forms/032_volleyball_player_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/032_volleyball_player_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -883,102 +883,102 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>position_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>setter</t>
+          <t>movement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Setter</t>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>position_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>libero</t>
+          <t>ball-handling</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Libero</t>
+          <t>Ball-Handling</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>position_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>right-side</t>
+          <t>blocking</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Right-Side</t>
+          <t>Blocking</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>position_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>middle-blocker</t>
+          <t>serving</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Middle-Blocker</t>
+          <t>Serving</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>position_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>left-side</t>
+          <t>passing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Left-Side</t>
+          <t>Passing</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>position_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>opposite</t>
+          <t>setting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Opposite</t>
+          <t>Setting</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>movement</t>
+          <t>spiking</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Spiking</t>
         </is>
       </c>
     </row>
@@ -1007,131 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ball-handling</t>
+          <t>digging</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ball-Handling</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>blocking</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Blocking</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>serving</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Serving</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>passing</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Passing</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>setting</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>spiking</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Spiking</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>digging</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>Digging</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>skills_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>blocking</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Blocking</t>
         </is>
       </c>
     </row>
